--- a/VT_REG1_ELCDMD_K03.xlsx
+++ b/VT_REG1_ELCDMD_K03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\VEDA_models\KModel_03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7DC1A6-6A52-451A-8845-70629CC129DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435C7D3A-3093-4186-82B1-E21B9DEB62CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{047E4344-2B87-4188-BA09-3302A30F5AF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{047E4344-2B87-4188-BA09-3302A30F5AF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t>Description</t>
   </si>
@@ -283,7 +283,13 @@
     <t>Electricity price - Dummy stand in for export</t>
   </si>
   <si>
-    <t>OUTPUT~ELC_PRIS</t>
+    <t>Selling the ELC_DEM</t>
+  </si>
+  <si>
+    <t>ELC_SELLING</t>
+  </si>
+  <si>
+    <t>Preparing for selling the electricity demand</t>
   </si>
 </sst>
 </file>
@@ -452,7 +458,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -473,9 +479,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,6 +660,89 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Tekstfelt 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B79905E-A8DE-779B-E511-6B894AD3FD8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10492740" y="160020"/>
+          <a:ext cx="1752600" cy="967740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="da-DK" sz="1100" kern="1200"/>
+            <a:t>ELC_SELLING is</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="da-DK" sz="1100" kern="1200" baseline="0"/>
+            <a:t> maybe not a DMD Sets? </a:t>
+          </a:r>
+          <a:endParaRPr lang="da-DK" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1024,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA31763-57A5-40A0-974A-970AFC6072D7}">
-  <dimension ref="B1:Q21"/>
+  <dimension ref="B1:P21"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="4"/>
@@ -1039,17 +1126,17 @@
     <col min="13" max="16384" width="10.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>21</v>
       </c>
@@ -1059,7 +1146,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="E6" s="9"/>
@@ -1070,7 +1157,7 @@
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="I7" s="9" t="s">
         <v>5</v>
       </c>
@@ -1082,7 +1169,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
     </row>
-    <row r="8" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
@@ -1114,25 +1201,22 @@
         <v>15</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="str">
         <f>Processes!D3</f>
         <v>ELC_DMD</v>
@@ -1150,9 +1234,7 @@
         <f>Commodities!D4</f>
         <v>ELC_DEM</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>69</v>
-      </c>
+      <c r="G9" s="5"/>
       <c r="H9" s="5">
         <v>2022</v>
       </c>
@@ -1163,29 +1245,59 @@
       <c r="K9" s="6">
         <v>1</v>
       </c>
-      <c r="L9" s="6">
-        <v>1</v>
-      </c>
+      <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
+      <c r="O9" s="5">
+        <v>50</v>
+      </c>
       <c r="P9" s="5">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="5">
         <f>8760*3.6/10^6</f>
         <v>3.1536000000000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L13" s="20"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L14" s="21"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="L15" s="22"/>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19">
+        <v>2022</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19">
+        <v>1</v>
+      </c>
+      <c r="K10" s="19">
+        <v>1</v>
+      </c>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19">
+        <v>50</v>
+      </c>
+      <c r="P10" s="5">
+        <f>8760*3.6/10^6</f>
+        <v>3.1536000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="L15" s="20"/>
     </row>
     <row r="21" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -1262,7 +1374,7 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>69</v>
@@ -1380,6 +1492,27 @@
         <v>38</v>
       </c>
     </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="19" t="str">
+        <f>Stocks!B10</f>
+        <v>ELC_SELLING</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H6" s="4" t="s">
         <v>68</v>
@@ -1392,6 +1525,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
